--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_CAQ.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_CAQ.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -544,7 +544,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>90.0</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>96.5</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-17.0</t>
+          <t>-6.5</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,11 @@
           <t>diff_fora</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -642,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q3 (-1)</t>
+          <t>Q1 (1)</t>
         </is>
       </c>
     </row>
@@ -659,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q1 (-6)</t>
+          <t>Q4 (-3.5)</t>
         </is>
       </c>
     </row>
@@ -675,11 +679,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -697,29 +701,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>períodos</t>
+          <t>home/away</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Melhor período: Q3 (-1)</t>
+          <t>Diff médio casa: -17 | fora: 4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>resultado</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Diff médio em vitórias: 4 | em derrotas: -17</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>períodos</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Pior período: Q1 (-6)</t>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Melhor período: Q1 (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>períodos</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pior período: Q4 (-3.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>player swing</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>I. Pavicevic sobe mais em vitórias (9 ppg).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B3"/>
+  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -730,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -794,38 +834,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>87</v>
+      </c>
+      <c r="E2" t="n">
+        <v>83</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>87</v>
+      </c>
+      <c r="H2" t="n">
+        <v>83</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
         <v>93</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E3" t="n">
         <v>110</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F3" t="n">
         <v>-17</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G3" t="n">
         <v>93</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H3" t="n">
         <v>110</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I3" t="n">
         <v>-17</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I2"/>
+  <autoFilter ref="A1:I3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -924,31 +997,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. Shoats</t>
+          <t>I. Pavicevic</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28.9</v>
+        <v>24.8</v>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>16</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
         <v>-9</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>25</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -965,193 +1052,291 @@
       <c r="D3" t="n">
         <v>-25</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>22</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
       <c r="J3" t="n">
         <v>17</v>
       </c>
       <c r="K3" t="n">
         <v>-25</v>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. Bacchus</t>
+          <t>D. Horta</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.6</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>-17</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>-15</v>
+      </c>
+      <c r="E4" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
       <c r="J4" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>-17</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+        <v>-15</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. Thomas</t>
+          <t>A. Hallman</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.7</v>
+        <v>11.2</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>-15</v>
+      </c>
+      <c r="E5" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
       <c r="J5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+        <v>-15</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. Ridgnal</t>
+          <t>D. Bacchus</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.1</v>
+        <v>26.6</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>-17</v>
+      </c>
+      <c r="E6" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+        <v>-17</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. Pavicevic</t>
+          <t>J. Thomas</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. Horta</t>
+          <t>D. Ridgnal</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>19.1</v>
       </c>
       <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F8" t="n">
         <v>5</v>
       </c>
-      <c r="D8" t="n">
-        <v>-15</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-8</v>
+      </c>
       <c r="J8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
         <v>5</v>
       </c>
-      <c r="K8" t="n">
-        <v>-15</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. Carneiro</t>
+          <t>J. Shoats</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14.4</v>
+        <v>28.9</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
+        <v>-9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>17</v>
+      </c>
+      <c r="G9" t="n">
+        <v>11</v>
+      </c>
+      <c r="H9" t="n">
+        <v>17</v>
+      </c>
+      <c r="I9" t="n">
+        <v>11</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" t="n">
         <v>-8</v>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M9"/>
@@ -1260,25 +1445,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G2" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="H2" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K2" t="n">
-        <v>-6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1303,25 +1488,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="H3" t="n">
         <v>-5</v>
       </c>
       <c r="I3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="J3" t="n">
         <v>23</v>
       </c>
-      <c r="J3" t="n">
-        <v>28</v>
-      </c>
       <c r="K3" t="n">
-        <v>-5</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="4">
@@ -1346,25 +1531,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="H4" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="I4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J4" t="n">
-        <v>29</v>
+        <v>26.5</v>
       </c>
       <c r="K4" t="n">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +1574,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="G5" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="H5" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="I5" t="n">
-        <v>22</v>
+        <v>20.5</v>
       </c>
       <c r="J5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>-5</v>
+        <v>-3.5</v>
       </c>
     </row>
   </sheetData>
@@ -1538,19 +1723,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1559,31 +1744,31 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1593,16 +1778,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1614,22 +1799,22 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1654,25 +1839,25 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -1681,16 +1866,16 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1699,96 +1884,96 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. Thomas</t>
+          <t>I. Pavicevic</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. Ridgnal</t>
+          <t>J. Thomas</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2</v>
       </c>
       <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K6" t="n">
         <v>2</v>
       </c>
-      <c r="D6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
@@ -1800,41 +1985,41 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. Pavicevic</t>
+          <t>D. Ridgnal</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1846,16 +2031,16 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1868,27 +2053,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1896,72 +2085,60 @@
       <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. Carneiro</t>
+          <t>A. Hallman</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>1</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q9" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q9"/>
@@ -1975,7 +2152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2053,8 +2230,37 @@
         <v>-17</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2922733</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>87</v>
+      </c>
+      <c r="F3" t="n">
+        <v>83</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_CAQ.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_CAQ.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -544,7 +544,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>84.8</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>91.2</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q1 (1)</t>
+          <t>Q2 (0.7)</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q4 (-3.5)</t>
+          <t>Q4 (-7)</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Melhor período: Q1 (1)</t>
+          <t>Melhor período: Q2 (0.7)</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pior período: Q4 (-3.5)</t>
+          <t>Pior período: Q4 (-7)</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>I. Pavicevic sobe mais em vitórias (9 ppg).</t>
+          <t>I. Pavicevic sobe mais em vitórias (11.5 ppg).</t>
         </is>
       </c>
     </row>
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>93</v>
+        <v>165</v>
       </c>
       <c r="E3" t="n">
-        <v>110</v>
+        <v>199</v>
       </c>
       <c r="F3" t="n">
-        <v>-17</v>
+        <v>-34</v>
       </c>
       <c r="G3" t="n">
-        <v>93</v>
+        <v>82.5</v>
       </c>
       <c r="H3" t="n">
-        <v>110</v>
+        <v>99.5</v>
       </c>
       <c r="I3" t="n">
         <v>-17</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24.8</v>
+        <v>18.9</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="E2" t="n">
         <v>26.2</v>
@@ -1025,16 +1025,16 @@
         <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L2" t="n">
-        <v>-9</v>
+        <v>-11.5</v>
       </c>
       <c r="M2" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="3">
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29.3</v>
+        <v>22.2</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="E3" t="n">
         <v>28.6</v>
@@ -1068,274 +1068,274 @@
         <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K3" t="n">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="L3" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. Horta</t>
+          <t>D. Bacchus</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>24.8</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-15</v>
+        <v>-13</v>
       </c>
       <c r="E4" t="n">
-        <v>21.1</v>
+        <v>30.2</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>-15</v>
+        <v>-13</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. Hallman</t>
+          <t>J. Shoats</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.2</v>
+        <v>29.9</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="D5" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
       <c r="E5" t="n">
-        <v>15.2</v>
+        <v>29.1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="K5" t="n">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. Bacchus</t>
+          <t>D. Horta</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.6</v>
+        <v>24.6</v>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>-17</v>
+        <v>-9.5</v>
       </c>
       <c r="E6" t="n">
-        <v>30.2</v>
+        <v>21.1</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>-17</v>
+        <v>-9.5</v>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. Thomas</t>
+          <t>D. Ridgnal</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.7</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="E7" t="n">
-        <v>32.1</v>
+        <v>10.7</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="M7" t="n">
-        <v>-4</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. Ridgnal</t>
+          <t>A. Hallman</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.1</v>
+        <v>18.3</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>-14.5</v>
       </c>
       <c r="E8" t="n">
-        <v>10.7</v>
+        <v>15.2</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>-14.5</v>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="M8" t="n">
-        <v>-5</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. Shoats</t>
+          <t>J. Thomas</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.9</v>
+        <v>27.2</v>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>-9</v>
+        <v>-4.5</v>
       </c>
       <c r="E9" t="n">
-        <v>29.1</v>
+        <v>32.1</v>
       </c>
       <c r="F9" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
-        <v>-9</v>
+        <v>-4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M9" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
     </row>
   </sheetData>
@@ -1445,25 +1445,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="G2" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>24</v>
+        <v>22.7</v>
       </c>
       <c r="J2" t="n">
-        <v>23</v>
+        <v>22.7</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1488,25 +1488,25 @@
         </is>
       </c>
       <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>70</v>
+      </c>
+      <c r="G3" t="n">
+        <v>68</v>
+      </c>
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="F3" t="n">
-        <v>41</v>
-      </c>
-      <c r="G3" t="n">
-        <v>46</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-5</v>
-      </c>
       <c r="I3" t="n">
-        <v>20.5</v>
+        <v>23.3</v>
       </c>
       <c r="J3" t="n">
-        <v>23</v>
+        <v>22.7</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="4">
@@ -1531,25 +1531,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="H4" t="n">
-        <v>-3</v>
+        <v>-11</v>
       </c>
       <c r="I4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
-        <v>26.5</v>
+        <v>23.7</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.5</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="5">
@@ -1574,25 +1574,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G5" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="H5" t="n">
+        <v>-21</v>
+      </c>
+      <c r="I5" t="n">
+        <v>18</v>
+      </c>
+      <c r="J5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K5" t="n">
         <v>-7</v>
-      </c>
-      <c r="I5" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>24</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-3.5</v>
       </c>
     </row>
   </sheetData>
@@ -1719,200 +1719,200 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. Shoats</t>
+          <t>A. Thiam</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. Thiam</t>
+          <t>J. Shoats</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.5</v>
+        <v>5.3</v>
       </c>
       <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
         <v>4</v>
       </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="N3" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. Bacchus</t>
+          <t>J. Thomas</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. Pavicevic</t>
+          <t>D. Bacchus</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1921,74 +1921,74 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. Thomas</t>
+          <t>I. Pavicevic</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7">
@@ -1998,28 +1998,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="D7" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -2053,37 +2053,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="9">
@@ -2108,37 +2108,53 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
       <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>1.5</v>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q9"/>
@@ -2152,7 +2168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2259,8 +2275,37 @@
         <v>4</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2922739</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>72</v>
+      </c>
+      <c r="F4" t="n">
+        <v>89</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-17</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>